--- a/data/processed/openrouter_rankings.xlsx
+++ b/data/processed/openrouter_rankings.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>197806801139</v>
+        <v>546094843364</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>20.54</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="3">
@@ -510,17 +510,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tencent</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>157821742834</v>
+        <v>446274880898</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>16.39</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="4">
@@ -534,17 +534,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>tencent</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>137602150819</v>
+        <v>392804974212</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>14.29</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="5">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>102527177148</v>
+        <v>313025648160</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>10.65</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="6">
@@ -582,17 +582,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>xiaomi</t>
+          <t>google</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80401806480</v>
+        <v>252291698386</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>8.35</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="7">
@@ -606,17 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>xiaomi</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75451450546</v>
+        <v>244675676626</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>7.83</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73948688103</v>
+        <v>230868981247</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>7.68</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="9">
@@ -654,17 +654,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55939312079</v>
+        <v>169678304456</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>5.81</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10">
@@ -678,17 +678,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48931796942</v>
+        <v>146905696516</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="11">
@@ -706,13 +706,493 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32608143545</v>
+        <v>89368958658</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.39</v>
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6746639180969</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>18.67</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5292323178165</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4587885098930</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4290526868557</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>minimax</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3045618468834</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>xiaomi</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2945645472735</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>tencent</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2942966551137</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.140000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2883841582934</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1948695944551</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1451168420478</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5603262102755</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17.61</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>anthropic</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5572164750921</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17.51</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4198365625686</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3825521459345</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12.02</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>tencent</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3027791032193</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2940629362850</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>xiaomi</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2813572539671</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1663748548920</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1213452606146</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>z-ai</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>962662909384</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>
@@ -1102,7 +1582,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pioneer (staging)</t>
+          <t>Pioneer (production)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1199,7 +1679,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Mira is the leading AI agent inside Telegram</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1300,7 +1780,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Sahasra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1533,7 +2013,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5033115957553</v>
+        <v>5213957358565</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1542,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>74607732</v>
+        <v>77403651</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1568,7 +2048,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1282970039620</v>
+        <v>1325873768513</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1577,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>25600733</v>
+        <v>26471107</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1603,7 +2083,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1244160309531</v>
+        <v>1296614903584</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1612,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>16389086</v>
+        <v>17119747</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1638,7 +2118,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>616429218661</v>
+        <v>644171050394</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1647,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7691942</v>
+        <v>8036999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1673,7 +2153,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>460555057346</v>
+        <v>473644586630</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1682,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6886518</v>
+        <v>7062520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1708,7 +2188,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>387495955537</v>
+        <v>396495212968</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1717,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6278117</v>
+        <v>6413481</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1743,7 +2223,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>321388869848</v>
+        <v>327761500740</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1752,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>9415409</v>
+        <v>9596808</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1774,7 +2254,7 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>270945669983</v>
+        <v>278789063509</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1783,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3274773</v>
+        <v>3389940</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1809,7 +2289,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>253760745254</v>
+        <v>254191642700</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1818,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2676050</v>
+        <v>2682120</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1844,7 +2324,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222029209923</v>
+        <v>229839200184</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1853,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>16300535</v>
+        <v>16868309</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1879,7 +2359,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>214033883030</v>
+        <v>220942444475</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1888,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5101622</v>
+        <v>5266387</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1914,7 +2394,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>169969348799</v>
+        <v>176050256438</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1923,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1887951</v>
+        <v>1960000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1949,7 +2429,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>132287372120</v>
+        <v>137606605837</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1958,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>14576471</v>
+        <v>15147934</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1984,7 +2464,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>129856106909</v>
+        <v>134680824229</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1993,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>11184746</v>
+        <v>11556952</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2010,12 +2490,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>llmv:sentiment</t>
+          <t>llmv:competitors</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>128327048123</v>
+        <v>129059612971</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2024,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>53175594</v>
+        <v>53492634</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2046,7 +2526,7 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>104575035071</v>
+        <v>109776467119</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2055,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1381257</v>
+        <v>1453309</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2081,7 +2561,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85329864962</v>
+        <v>90753602517</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2090,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1999576</v>
+        <v>2080244</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2107,12 +2587,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AA-LCR Benchmark</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>75516001597</v>
+        <v>77805388062</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2121,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>12904962</v>
+        <v>936763</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2138,16 +2622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Codex</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
+          <t>AA-LCR Benchmark</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>75245520835</v>
+        <v>76781470058</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2156,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>904136</v>
+        <v>13195782</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2182,7 +2662,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>62375420715</v>
+        <v>64331881773</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2191,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3685591</v>
+        <v>3797143</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2278,7 +2758,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15065045151987</v>
+        <v>15245889485193</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2287,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>236049428</v>
+        <v>238845400</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2313,7 +2793,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5064312273440</v>
+        <v>5107216372508</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -2322,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>103954909</v>
+        <v>104825290</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2348,7 +2828,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4570392020281</v>
+        <v>4622846783962</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2357,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>65850778</v>
+        <v>66581444</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2383,7 +2863,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1871566601033</v>
+        <v>1899309072477</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2392,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>23672124</v>
+        <v>24017189</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2418,7 +2898,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1720242916060</v>
+        <v>1733332473722</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2427,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>27649835</v>
+        <v>27825839</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -2453,7 +2933,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1334106924036</v>
+        <v>1343106181467</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2462,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>22397251</v>
+        <v>22532615</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2488,7 +2968,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>884238021760</v>
+        <v>892048264422</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2497,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>67419595</v>
+        <v>67987389</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2523,7 +3003,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>808445406617</v>
+        <v>814818214247</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2532,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>21851733</v>
+        <v>22033137</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2558,7 +3038,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>799814813951</v>
+        <v>806723585317</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2567,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>21853167</v>
+        <v>22017933</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2593,7 +3073,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>637547674404</v>
+        <v>643628716145</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2602,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7343424</v>
+        <v>7415475</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2628,7 +3108,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>589852158178</v>
+        <v>590283121779</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2637,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6184803</v>
+        <v>6190874</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2659,7 +3139,7 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>535117234992</v>
+        <v>542960919604</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2668,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8333102</v>
+        <v>8448273</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2694,7 +3174,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>493463869490</v>
+        <v>495625920866</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2703,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5521877</v>
+        <v>5545498</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2729,7 +3209,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>454372085066</v>
+        <v>459196876556</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2738,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>33230521</v>
+        <v>33602729</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2751,7 +3231,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2764,7 +3244,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248270196176</v>
+        <v>253589494286</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2773,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>27439666</v>
+        <v>28011141</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2786,7 +3266,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2799,7 +3279,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>247610955599</v>
+        <v>249567427108</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2808,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>14910664</v>
+        <v>15022217</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2830,7 +3310,7 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>215691946633</v>
+        <v>216957438580</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2839,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>15368022</v>
+        <v>15658846</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2856,16 +3336,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>OpenHands</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>langchain</t>
+          <t>openhands</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>207917483514</v>
+        <v>211598589767</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2874,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>24826989</v>
+        <v>5366940</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2891,16 +3371,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OpenHands</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>openhands</t>
+          <t>langchain</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206174796871</v>
+        <v>209384743669</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2909,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5286271</v>
+        <v>25293388</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2935,7 +3415,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>195109882538</v>
+        <v>195111701368</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2944,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3906786</v>
+        <v>3906997</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2961,7 +3441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3011,13 +3491,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>333507961297</v>
+        <v>1035136952921</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>34.65</v>
+        <v>36.55</v>
       </c>
     </row>
     <row r="3">
@@ -3035,13 +3515,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>157741704812</v>
+        <v>392797638390</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>16.39</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="4">
@@ -3059,13 +3539,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>116448867565</v>
+        <v>320520825141</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="5">
@@ -3083,13 +3563,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68387376885</v>
+        <v>210511946302</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>7.1</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="6">
@@ -3107,13 +3587,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64290758771</v>
+        <v>198423108278</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>6.68</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="7">
@@ -3127,17 +3607,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>openrouter/owl-alpha</t>
+          <t>anthropic/claude-4.7-opus-20260416</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55916589433</v>
+        <v>150652129237</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>5.81</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="8">
@@ -3151,17 +3631,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>anthropic/claude-4.7-opus-20260416</t>
+          <t>openrouter/owl-alpha</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51455272271</v>
+        <v>146902491354</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>5.35</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="9">
@@ -3179,7 +3659,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48547013854</v>
+        <v>142653624253</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -3203,13 +3683,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38111862094</v>
+        <v>135284743106</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>3.96</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="11">
@@ -3223,17 +3703,737 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v3.2-20251201</t>
+          <t>anthropic/claude-4.8-opus-20260528</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28125032517</v>
+        <v>99054489298</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4093614471177</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49.62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.5-sonnet-20250929</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>774547335543</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.390000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>google/gemini-3-flash-preview-20251217</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>688836171168</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>507333780688</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>x-ai/grok-code-fast-1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>421626971930</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>405901304680</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.5-opus-20251124</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>377870999007</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>moonshotai/kimi-k2.5-0127</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>359303717844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>x-ai/grok-4.1-fast</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>316457561436</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>304442038445</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3295602940648</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>56.43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>x-ai/grok-code-fast-1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>517261241082</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8.859999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>438708651368</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.5-sonnet-20250929</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>416299356874</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>220245506891</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.5-opus-20251124</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>209253116284</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>205450473114</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>google/gemini-2.0-flash-001</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>184561836303</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>182341260426</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>xiaomi/mimo-v2-flash-20251210:free</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>170776227913</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
         <v>2.92</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3062471941313</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>53.05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>x-ai/grok-code-fast-1</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>618469718813</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>453242014019</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.5-sonnet-20250929</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>430777771586</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>323018614438</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.5-opus-20251124</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>211974303282</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>google/gemini-2.0-flash-001</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>189082856905</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>168402695203</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>x-ai/grok-4-fast</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>159985083087</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-pro</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>155321637073</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.69</v>
       </c>
     </row>
   </sheetData>
@@ -13918,7 +15118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14191,6 +15391,726 @@
       </c>
       <c r="F11" t="n">
         <v>3.22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3777907884300</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.78</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-20260423</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>855876830400</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.7-opus-20260416</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>736615336000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.539999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>tencent/hy3-preview-20260421</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>654398555200</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>moonshotai/kimi-k2.6-20260420</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>524305629600</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-sonnet-20260217</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>475307845600</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>stepfun/step-3.5-flash</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>470917896000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-super-120b-a12b-20230311:free</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>430379947200</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-pro-20260423</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>412275704000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.5-20260423</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>291011918400</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2313746063700</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.6-plus-04-02:free</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1562705036000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19.21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>minimax/minimax-m2.7-20260318</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1050672240800</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>minimax/minimax-m2.5-20260211</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>754087272000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-opus-20260205</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>609118429600</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nvidia/nemotron-3-super-120b-a12b-20230311:free</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>437255952000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>moonshotai/kimi-k2.5-0127</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>412849775200</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5-20260211</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>371996948800</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-sonnet-20260217</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>332789710400</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.4-20260305</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>287991325600</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>minimax/minimax-m2.5-20260211</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1739039162400</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>34.76</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1204327312700</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>24.07</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>moonshotai/kimi-k2.5-0127</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>522240354400</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10.44</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-opus-20260205</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>395219200000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>google/gemini-3-flash-preview-20251217</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>260664137600</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-sonnet-20260217</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>248502188000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.2-20251211</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>205288900800</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>stepfun/step-3.5-flash:free</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>163566852800</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5-20260211</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>134716876000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.3-codex-20260224</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>129219516000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.58</v>
       </c>
     </row>
   </sheetData>
@@ -14204,7 +16124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14254,13 +16174,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8109136</v>
+        <v>46416033</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>54.51</v>
+        <v>56.57</v>
       </c>
     </row>
     <row r="3">
@@ -14278,13 +16198,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1155006</v>
+        <v>6492110</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>7.76</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="4">
@@ -14298,17 +16218,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash-lite</t>
+          <t>google/gemini-2.5-flash</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>955186</v>
+        <v>6270652</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>6.42</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="5">
@@ -14322,17 +16242,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash</t>
+          <t>google/gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>861384</v>
+        <v>5502422</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>5.79</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="6">
@@ -14346,17 +16266,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v3.2-20251201</t>
+          <t>google/gemini-3-flash-preview-20251217</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>763931</v>
+        <v>3783864</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>5.14</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="7">
@@ -14370,17 +16290,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>google/gemini-3-flash-preview-20251217</t>
+          <t>deepseek/deepseek-v3.2-20251201</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>672523</v>
+        <v>3610055</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="8">
@@ -14394,17 +16314,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.5-air</t>
+          <t>google/gemini-3.1-flash-lite-20260507</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>632730</v>
+        <v>2568605</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>4.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="9">
@@ -14418,17 +16338,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>google/gemini-3.1-flash-lite-20260507</t>
+          <t>mistralai/mistral-nemo</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>605561</v>
+        <v>2510349</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>4.07</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="10">
@@ -14442,17 +16362,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mistralai/mistral-nemo</t>
+          <t>meta-llama/llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>561406</v>
+        <v>2456676</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>3.77</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="11">
@@ -14466,17 +16386,497 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3.1-8b-instruct</t>
+          <t>openai/gpt-oss-120b</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>558206</v>
+        <v>2433078</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.75</v>
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>801382674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>52.79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>108896617</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-20260423</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>105598209</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>103068801</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>meta-llama/llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>79860116</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>google/gemini-3-flash-preview-20251217</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>68274860</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>qwen/qwen3-235b-a22b-07-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>66299591</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>63898120</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>60881523</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>openai/gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>59910911</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>742994026</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>54.19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>115043047</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-20260423</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>97119802</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>84005086</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>google/gemini-3-flash-preview-20251217</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>67217060</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>60777400</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>58671124</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>z-ai/glm-4.5-air</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>55258817</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>openai/gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>48550272</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>meta-llama/llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>41520110</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.03</v>
       </c>
     </row>
   </sheetData>
@@ -14490,7 +16890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14763,6 +17163,726 @@
       </c>
       <c r="F11" t="n">
         <v>3.73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>783445051166.6664</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49.14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-20260423</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>149159492000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>tencent/hy3-preview-20260421</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>131472956000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>minimax/minimax-m3-20260531</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>99522644000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>94415353333.3333</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-pro-20260423</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>89959261333.33334</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-sonnet-20260217</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>77833412000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.5-20260423</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>59674484000.00002</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>xiaomi/mimo-v2.5-20260422</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>58992129333.33334</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.8-opus-20260528</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>49855946666.66667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>602691136666.667</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>41.78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-20260423</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>214338297333.3333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14.86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>tencent/hy3-preview-20260421</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>165926112000.0001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.7-opus-20260416</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>90153494666.66666</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-pro-20260423</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>82717061333.33333</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>openrouter/owl-alpha</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>76828817333.3333</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-sonnet-20260217</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>74768898666.66666</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>62723026666.66667</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>google/gemini-3-flash-preview-20251217</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>39130451999.99999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.5-20260423</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>33216314666.66667</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>714626658666.667</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-20260423</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>299742963999.9999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>18.16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>tencent/hy3-preview-20260421</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>152811530666.6667</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.7-opus-20260416</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>114859489333.3333</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>anthropic/claude-4.6-sonnet-20260217</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>100540692000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-pro-20260423</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>75872026666.66666</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v3.2-20251201</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>64990302666.66667</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>google/gemini-3-flash-preview-20251217</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>47177525333.33334</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.5-20260423</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>40090000000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>39872288000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.42</v>
       </c>
     </row>
   </sheetData>
